--- a/results/02_taxa_assemblage/MRT_Method/classifier_prediction/tables/mrt_predictions.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/classifier_prediction/tables/mrt_predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B176"/>
+  <dimension ref="A1:B181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -717,23 +717,23 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>059ABC</t>
+          <t>057C</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>067B</t>
+          <t>059ABC</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -743,7 +743,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>069A</t>
+          <t>067B</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -753,7 +753,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>070B</t>
+          <t>069A</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -763,47 +763,47 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>072A</t>
+          <t>070B</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>074B</t>
+          <t>072A</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>075A</t>
+          <t>074B</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>076ABC</t>
+          <t>075A</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>079C</t>
+          <t>076ABC</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -813,27 +813,27 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>080C</t>
+          <t>079C</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>081B</t>
+          <t>080C</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>082A</t>
+          <t>081B</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -843,27 +843,27 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>083B</t>
+          <t>082A</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>084A</t>
+          <t>083B</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>085C</t>
+          <t>084A</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -873,7 +873,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>086A</t>
+          <t>085C</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -883,77 +883,77 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>088C</t>
+          <t>086A</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>089A</t>
+          <t>088C</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>090B</t>
+          <t>089A</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>091C</t>
+          <t>090B</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>092ABC</t>
+          <t>091C</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>093C</t>
+          <t>092ABC</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>095A</t>
+          <t>093C</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>096A</t>
+          <t>095A</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -963,7 +963,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>099C</t>
+          <t>096A</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -973,7 +973,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>099C</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -983,7 +983,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>101C</t>
+          <t>100C</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -993,47 +993,47 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>102B</t>
+          <t>101C</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>103A</t>
+          <t>102B</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>104C</t>
+          <t>103A</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>105C</t>
+          <t>104C</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>106B</t>
+          <t>105C</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1043,7 +1043,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>107C</t>
+          <t>106B</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1053,7 +1053,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>108B</t>
+          <t>107C</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1063,27 +1063,27 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>113B</t>
+          <t>108B</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>115ABC</t>
+          <t>113B</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>116B</t>
+          <t>114B</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1093,37 +1093,37 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>118A</t>
+          <t>115ABC</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>119B</t>
+          <t>116B</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>123A</t>
+          <t>118A</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>124A</t>
+          <t>119B</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1133,37 +1133,37 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>126A</t>
+          <t>123A</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>127B</t>
+          <t>124A</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>128B</t>
+          <t>126A</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>129A</t>
+          <t>127B</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1173,97 +1173,97 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>130A</t>
+          <t>128B</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>131B</t>
+          <t>129A</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>132B</t>
+          <t>130A</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>134C</t>
+          <t>131B</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>135A</t>
+          <t>132B</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>136B</t>
+          <t>134C</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>137A</t>
+          <t>135A</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>138B</t>
+          <t>136B</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>140C</t>
+          <t>137A</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>142C</t>
+          <t>138B</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1273,57 +1273,57 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>143B</t>
+          <t>140C</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>144B</t>
+          <t>142C</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>145B</t>
+          <t>143B</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>147A</t>
+          <t>144B</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>148B</t>
+          <t>145B</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>149C</t>
+          <t>147A</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -1333,17 +1333,17 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>148B</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>149C</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -1353,77 +1353,77 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A28</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A53</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>A58</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -1433,7 +1433,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>DBC2</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -1443,47 +1443,47 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>DCC2</t>
+          <t>A66</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>DCE3</t>
+          <t>DBC2</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>DJC2</t>
+          <t>DCC2</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>MCE2</t>
+          <t>DCE3</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DJC2</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -1493,17 +1493,17 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>MCE2</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>S100</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -1513,27 +1513,27 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>S101</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>S100</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S101</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -1543,47 +1543,47 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S102</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -1593,37 +1593,37 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -1633,17 +1633,17 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>S21(5)</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -1653,17 +1653,17 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S21(5)</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -1673,17 +1673,17 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>S27(5)</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -1693,37 +1693,37 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S27(5)</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>S40</t>
+          <t>S28(5)</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -1733,37 +1733,37 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>S40</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -1773,7 +1773,7 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>S46</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -1783,17 +1783,17 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -1803,7 +1803,7 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S46</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -1813,27 +1813,27 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S48</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -1843,7 +1843,7 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -1853,7 +1853,7 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>S58</t>
+          <t>S50</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -1863,47 +1863,47 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>S57</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>S58</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>S63</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -1913,7 +1913,7 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>S64</t>
+          <t>S60</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -1923,47 +1923,47 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>S66</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>S67</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>S68</t>
+          <t>S63</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>S74</t>
+          <t>S64</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>S78</t>
+          <t>S66</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1973,7 +1973,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>S67</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1983,7 +1983,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S68</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -1993,17 +1993,17 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>S80</t>
+          <t>S69</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>S82</t>
+          <t>S74</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -2013,17 +2013,17 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>S83</t>
+          <t>S78</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>S84</t>
+          <t>S79</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -2033,27 +2033,27 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>S85</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>S87</t>
+          <t>S80</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>S89</t>
+          <t>S82</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -2063,17 +2063,17 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S83</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>S90</t>
+          <t>S84</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -2083,7 +2083,7 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>S93</t>
+          <t>S85</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -2093,7 +2093,7 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>S94</t>
+          <t>S87</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -2103,17 +2103,17 @@
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>S95</t>
+          <t>S89</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>S96</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -2123,7 +2123,7 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>S97</t>
+          <t>S90</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -2133,60 +2133,110 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>S98</t>
+          <t>S93</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>S99</t>
+          <t>S94</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>UBC1</t>
+          <t>S95</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>UCC1</t>
+          <t>S96</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>UCE1</t>
+          <t>S97</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
+          <t>S98</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>S99</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>UBC1</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>UCC1</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>UCE1</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
           <t>UJC1</t>
         </is>
       </c>
-      <c r="B176" t="n">
+      <c r="B181" t="n">
         <v>3</v>
       </c>
     </row>

--- a/results/02_taxa_assemblage/MRT_Method/classifier_prediction/tables/mrt_predictions.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/classifier_prediction/tables/mrt_predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B181"/>
+  <dimension ref="A1:B189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -537,23 +537,23 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>021B</t>
+          <t>018A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>022B</t>
+          <t>019B</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -563,7 +563,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>023C</t>
+          <t>021B</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -573,17 +573,17 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>024C</t>
+          <t>022B</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>027B</t>
+          <t>023C</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -593,17 +593,17 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>029C</t>
+          <t>024C</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>031A</t>
+          <t>025B</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -613,37 +613,37 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>034C</t>
+          <t>027B</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>037B</t>
+          <t>029C</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>042C</t>
+          <t>031A</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>044A</t>
+          <t>034C</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -653,17 +653,17 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>045B</t>
+          <t>037B</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>047ABC</t>
+          <t>042C</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -673,17 +673,17 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>048C</t>
+          <t>043ABC</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>049A</t>
+          <t>044A</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -693,7 +693,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>052B</t>
+          <t>045B</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -703,87 +703,87 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>054B</t>
+          <t>047ABC</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>055C</t>
+          <t>048C</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>057C</t>
+          <t>049A</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>059ABC</t>
+          <t>052B</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>067B</t>
+          <t>054B</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>069A</t>
+          <t>055C</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>070B</t>
+          <t>057C</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>072A</t>
+          <t>059ABC</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>074B</t>
+          <t>065C</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -793,17 +793,17 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>075A</t>
+          <t>067B</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>076ABC</t>
+          <t>069A</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -813,7 +813,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>079C</t>
+          <t>070B</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -823,7 +823,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>080C</t>
+          <t>072A</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -833,7 +833,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>081B</t>
+          <t>074B</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -843,47 +843,47 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>082A</t>
+          <t>075A</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>083B</t>
+          <t>076ABC</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>084A</t>
+          <t>077B</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>085C</t>
+          <t>078B</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>086A</t>
+          <t>079C</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -893,17 +893,17 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>088C</t>
+          <t>080C</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>089A</t>
+          <t>081B</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -913,7 +913,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>090B</t>
+          <t>082A</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -923,27 +923,27 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>091C</t>
+          <t>083B</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>092ABC</t>
+          <t>084A</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>093C</t>
+          <t>085C</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -953,47 +953,47 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>095A</t>
+          <t>086A</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>096A</t>
+          <t>088C</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>099C</t>
+          <t>089A</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>090B</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>101C</t>
+          <t>091C</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1003,57 +1003,57 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>102B</t>
+          <t>092ABC</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>103A</t>
+          <t>093C</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>104C</t>
+          <t>094C</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>105C</t>
+          <t>095A</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>106B</t>
+          <t>096A</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>107C</t>
+          <t>097ABC</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1063,17 +1063,17 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>108B</t>
+          <t>098C</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>113B</t>
+          <t>099C</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1083,7 +1083,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>114B</t>
+          <t>100C</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1093,7 +1093,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>115ABC</t>
+          <t>101C</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1103,17 +1103,17 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>116B</t>
+          <t>102B</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>118A</t>
+          <t>103A</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1123,17 +1123,17 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>119B</t>
+          <t>104C</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>123A</t>
+          <t>105C</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1143,7 +1143,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>124A</t>
+          <t>106B</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1153,177 +1153,177 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>126A</t>
+          <t>107C</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>127B</t>
+          <t>108B</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>128B</t>
+          <t xml:space="preserve">111C </t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>129A</t>
+          <t>113B</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>130A</t>
+          <t>114B</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>131B</t>
+          <t>115ABC</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>132B</t>
+          <t>116B</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>134C</t>
+          <t>117ABC</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>135A</t>
+          <t>118A</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>136B</t>
+          <t>119B</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>137A</t>
+          <t>123A</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>138B</t>
+          <t>124A</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>140C</t>
+          <t>126A</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>142C</t>
+          <t>127B</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>143B</t>
+          <t>128B</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>144B</t>
+          <t>129A</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>145B</t>
+          <t>130A</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>147A</t>
+          <t>131B</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -1333,7 +1333,7 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>148B</t>
+          <t>132B</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -1343,17 +1343,17 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>149C</t>
+          <t>134C</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>135A</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -1363,17 +1363,17 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>136B</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>137A</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -1383,27 +1383,27 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>138B</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>140C</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>141B</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1413,7 +1413,7 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>142C</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -1423,7 +1423,7 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>143B</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -1433,27 +1433,27 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>144B</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>145B</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>DBC2</t>
+          <t>146B</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -1463,7 +1463,7 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>DCC2</t>
+          <t>147A</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -1473,7 +1473,7 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>DCE3</t>
+          <t>148B</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -1483,107 +1483,107 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>DJC2</t>
+          <t>149C</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>MCE2</t>
+          <t>150B</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>S100</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>S101</t>
+          <t>A28</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>A53</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>A58</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -1593,7 +1593,7 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>A66</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -1603,37 +1603,37 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>DBC2</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>DCC2</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DCE3</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>DJC2</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -1643,27 +1643,27 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>MCE2</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>S21(5)</t>
+          <t>S100</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -1673,17 +1673,17 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S101</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S102</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -1693,27 +1693,27 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>S27(5)</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -1723,47 +1723,47 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>S40</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -1773,77 +1773,77 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S21(5)</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>S46</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S27(5)</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S28(5)</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -1853,7 +1853,7 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -1863,37 +1863,37 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S40</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>S58</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -1903,17 +1903,17 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -1923,87 +1923,87 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>S46</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>S63</t>
+          <t>S48</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>S64</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>S66</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>S67</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>S68</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>S57</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>S74</t>
+          <t>S58</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -2013,17 +2013,17 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>S78</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>S60</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -2033,27 +2033,27 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>S80</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>S82</t>
+          <t>S63</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -2063,27 +2063,27 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>S83</t>
+          <t>S64</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>S84</t>
+          <t>S66</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>S85</t>
+          <t>S67</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -2093,17 +2093,17 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>S87</t>
+          <t>S68</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>S89</t>
+          <t>S78</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -2113,7 +2113,7 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S79</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -2123,7 +2123,7 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>S90</t>
+          <t>S80</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -2133,17 +2133,17 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>S93</t>
+          <t>S82</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>S94</t>
+          <t>S83</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -2153,7 +2153,7 @@
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>S95</t>
+          <t>S84</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -2163,17 +2163,17 @@
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>S96</t>
+          <t>S85</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>S97</t>
+          <t>S87</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -2183,47 +2183,47 @@
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>S98</t>
+          <t>S89</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>S99</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>UBC1</t>
+          <t>S90</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>UCC1</t>
+          <t>S93</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>UCE1</t>
+          <t>S94</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -2233,10 +2233,90 @@
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
+          <t>S95</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>S96</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>S97</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>S98</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>S99</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>UBC1</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>UCC1</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>UCE1</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
           <t>UJC1</t>
         </is>
       </c>
-      <c r="B181" t="n">
+      <c r="B189" t="n">
         <v>3</v>
       </c>
     </row>
